--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-visdrone.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-visdrone.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>3333.572754859924</v>
+        <v>10887.41858506203</v>
       </c>
       <c r="D2" t="n">
-        <v>7.28000020980835</v>
+        <v>15.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2013163644431242</v>
+        <v>0.5314450934529305</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5078007578849792</v>
+        <v>0.5643786191940308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4755111038684845</v>
+        <v>0.5322831869125366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4747897386550903</v>
+        <v>0.5324639081954956</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4751509428024292</v>
+        <v>0.5326173901557922</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0949224680662155</v>
+        <v>0.1828881651163101</v>
       </c>
       <c r="K2" t="n">
-        <v>100.1189095973968</v>
+        <v>654.8975448608398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0544432441393534</v>
+        <v>0.0920556871096293</v>
       </c>
       <c r="M2" t="n">
-        <v>0.072392303943634</v>
+        <v>0.458036306699117</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0675287429491678</v>
+        <v>0.1462067294120788</v>
       </c>
       <c r="O2" t="n">
-        <v>16.33297324180603</v>
+        <v>27.6167061328888</v>
       </c>
       <c r="P2" t="n">
-        <v>21.71769118309021</v>
+        <v>137.4108920097351</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.25862288475037</v>
+        <v>43.86201882362366</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-185631</t>
+          <t>20250726-074846</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>2687.849930286407</v>
+        <v>8029.952249526978</v>
       </c>
       <c r="D3" t="n">
-        <v>7.309999942779541</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2002620073380293</v>
+        <v>0.5314940243232541</v>
       </c>
       <c r="F3" t="n">
-        <v>0.500224232673645</v>
+        <v>0.5629640817642212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4734110534191131</v>
+        <v>0.528606653213501</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4737220406532287</v>
+        <v>0.5293181538581848</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4724377989768982</v>
+        <v>0.5279617309570312</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1017721444368362</v>
+        <v>0.1805954873561859</v>
       </c>
       <c r="K3" t="n">
-        <v>101.1841666698456</v>
+        <v>648.6885213851929</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0571118172009786</v>
+        <v>0.0918305253982544</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0706735587120056</v>
+        <v>0.4546645283699035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0686127074559529</v>
+        <v>0.1456816005706787</v>
       </c>
       <c r="O3" t="n">
-        <v>17.13354516029358</v>
+        <v>27.54915761947632</v>
       </c>
       <c r="P3" t="n">
-        <v>21.20206761360168</v>
+        <v>136.3993585109711</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.58381223678589</v>
+        <v>43.70448017120361</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-195525</t>
+          <t>20250726-110530</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>3009.614695072174</v>
+        <v>10686.18502807617</v>
       </c>
       <c r="D4" t="n">
-        <v>7.269999980926514</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1993505534578541</v>
+        <v>0.5304153128103777</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5077049732208252</v>
+        <v>0.5651895999908447</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4778015911579132</v>
+        <v>0.5296593308448792</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4784354269504547</v>
+        <v>0.5294935703277588</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4773849248886108</v>
+        <v>0.5285189151763916</v>
       </c>
       <c r="J4" t="n">
-        <v>0.101452462375164</v>
+        <v>0.1813321113586425</v>
       </c>
       <c r="K4" t="n">
-        <v>101.611344575882</v>
+        <v>657.8846120834351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0548339525858561</v>
+        <v>0.0921697751681009</v>
       </c>
       <c r="M4" t="n">
-        <v>0.070663358370463</v>
+        <v>0.4543225717544555</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0676269308725992</v>
+        <v>0.1459953530629475</v>
       </c>
       <c r="O4" t="n">
-        <v>16.45018577575684</v>
+        <v>27.65093255043029</v>
       </c>
       <c r="P4" t="n">
-        <v>21.19900751113892</v>
+        <v>136.2967715263367</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.28807926177979</v>
+        <v>43.79860591888428</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-204334</t>
+          <t>20250726-133429</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>3628.10049700737</v>
+        <v>10496.89358711243</v>
       </c>
       <c r="D5" t="n">
-        <v>7.260000228881836</v>
+        <v>15.48999977111816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2008665640876717</v>
+        <v>0.5309874768610354</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5135114789009094</v>
+        <v>0.5626495480537415</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4852354228496551</v>
+        <v>0.528397798538208</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4859492182731628</v>
+        <v>0.5294328331947327</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4844407141208648</v>
+        <v>0.5270232558250427</v>
       </c>
       <c r="J5" t="n">
-        <v>0.096487246453762</v>
+        <v>0.1815173774957656</v>
       </c>
       <c r="K5" t="n">
-        <v>101.1971869468689</v>
+        <v>633.9037442207336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0553350289662679</v>
+        <v>0.0917146182060241</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0711675302187601</v>
+        <v>0.4558455069859822</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0686814864476521</v>
+        <v>0.1444210990269978</v>
       </c>
       <c r="O5" t="n">
-        <v>16.60050868988037</v>
+        <v>27.51438546180725</v>
       </c>
       <c r="P5" t="n">
-        <v>21.35025906562805</v>
+        <v>136.7536520957947</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.60444593429565</v>
+        <v>43.32632970809937</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-213705</t>
+          <t>20250726-164754</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>3227.192258358002</v>
+        <v>9158.685127735138</v>
       </c>
       <c r="D6" t="n">
-        <v>7.210000038146973</v>
+        <v>15.52999973297119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2007171795918391</v>
+        <v>0.530693974900753</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5094115734100342</v>
+        <v>0.5642752647399902</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4765693247318268</v>
+        <v>0.5306106209754944</v>
       </c>
       <c r="H6" t="n">
-        <v>0.477531224489212</v>
+        <v>0.5308862924575806</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4771215617656708</v>
+        <v>0.5312674641609192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0929730236530304</v>
+        <v>0.1819579005241394</v>
       </c>
       <c r="K6" t="n">
-        <v>103.1360576152802</v>
+        <v>632.0662925243378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0552577527364095</v>
+        <v>0.0925037384033203</v>
       </c>
       <c r="M6" t="n">
-        <v>0.072851345539093</v>
+        <v>0.4615024852752685</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0682937320073445</v>
+        <v>0.1470043563842773</v>
       </c>
       <c r="O6" t="n">
-        <v>16.57732582092285</v>
+        <v>27.75112152099609</v>
       </c>
       <c r="P6" t="n">
-        <v>21.85540366172791</v>
+        <v>138.4507455825806</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.48811960220337</v>
+        <v>44.1013069152832</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-224055</t>
+          <t>20250726-195746</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>6969.898000955582</v>
+        <v>3585.009848833084</v>
       </c>
       <c r="D2" t="n">
-        <v>10.17000007629394</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3126057375754629</v>
+        <v>0.6442301846467532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5636123418807983</v>
+        <v>0.5926007628440857</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5318695306777954</v>
+        <v>0.5600462555885315</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5304054021835327</v>
+        <v>0.5606423020362854</v>
       </c>
       <c r="I2" t="n">
-        <v>0.528699517250061</v>
+        <v>0.5560928583145142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1357060372829437</v>
+        <v>0.149572417140007</v>
       </c>
       <c r="K2" t="n">
-        <v>657.9425008296967</v>
+        <v>1108.092591762543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0841900825500488</v>
+        <v>0.1188545433680216</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4534815184275309</v>
+        <v>0.1833109935124715</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1458669543266296</v>
+        <v>0.1213250041007995</v>
       </c>
       <c r="O2" t="n">
-        <v>25.25702476501465</v>
+        <v>35.65636301040649</v>
       </c>
       <c r="P2" t="n">
-        <v>136.0444555282593</v>
+        <v>54.99329805374146</v>
       </c>
       <c r="Q2" t="n">
-        <v>43.76008629798889</v>
+        <v>36.39750123023987</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-133201</t>
+          <t>20250725-092302</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>8235.00825381279</v>
+        <v>10436.73432254791</v>
       </c>
       <c r="D3" t="n">
-        <v>10.22999954223633</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3145670534083337</v>
+        <v>0.6420452109972636</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5641696453094482</v>
+        <v>0.6313254833221436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5339586138725281</v>
+        <v>0.5945160388946533</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5345724821090698</v>
+        <v>0.5947372317314148</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5346479415893555</v>
+        <v>0.5899081230163574</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1365142166614532</v>
+        <v>0.1514999866485595</v>
       </c>
       <c r="K3" t="n">
-        <v>732.1931021213531</v>
+        <v>1106.944672346115</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08517828385035189</v>
+        <v>0.1211755506197611</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4568185424804687</v>
+        <v>0.1861524113019307</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1480657792091369</v>
+        <v>0.1242534478505452</v>
       </c>
       <c r="O3" t="n">
-        <v>25.55348515510559</v>
+        <v>36.35266518592834</v>
       </c>
       <c r="P3" t="n">
-        <v>137.0455627441406</v>
+        <v>55.84572339057922</v>
       </c>
       <c r="Q3" t="n">
-        <v>44.41973376274109</v>
+        <v>37.27603435516357</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-154328</t>
+          <t>20250725-104430</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>6970.995094776154</v>
+        <v>8870.692751407623</v>
       </c>
       <c r="D4" t="n">
-        <v>10.10000038146973</v>
+        <v>23.1299991607666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3129776215979031</v>
+        <v>0.640429519471668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5634840130805969</v>
+        <v>0.638245701789856</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5294604897499084</v>
+        <v>0.6040176749229431</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5287261605262756</v>
+        <v>0.6058322191238403</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5275395512580872</v>
+        <v>0.599291980266571</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1324775069952011</v>
+        <v>0.1525907963514328</v>
       </c>
       <c r="K4" t="n">
-        <v>662.4461476802826</v>
+        <v>1109.100537538528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0839404241243998</v>
+        <v>0.1227410078048706</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4557456413904825</v>
+        <v>0.1862886198361714</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1464077719052632</v>
+        <v>0.1233907357851664</v>
       </c>
       <c r="O4" t="n">
-        <v>25.18212723731994</v>
+        <v>36.82230234146118</v>
       </c>
       <c r="P4" t="n">
-        <v>136.7236924171448</v>
+        <v>55.88658595085144</v>
       </c>
       <c r="Q4" t="n">
-        <v>43.92233157157898</v>
+        <v>37.01722073554993</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-181716</t>
+          <t>20250725-140012</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>6029.753540754318</v>
+        <v>4991.841129779816</v>
       </c>
       <c r="D5" t="n">
-        <v>10.17000007629394</v>
+        <v>23.17000007629395</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3163145979245503</v>
+        <v>0.6397438151495797</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5614874958992004</v>
+        <v>0.6156542301177979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5293604135513306</v>
+        <v>0.5769259333610535</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5293813943862915</v>
+        <v>0.5775007605552673</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5290794968605042</v>
+        <v>0.5741488933563232</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1314723044633865</v>
+        <v>0.1412497013807296</v>
       </c>
       <c r="K5" t="n">
-        <v>658.7847328186035</v>
+        <v>1108.07759141922</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0840928824742635</v>
+        <v>0.1183104912439982</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4616329765319824</v>
+        <v>0.1862595129013061</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1457098786036173</v>
+        <v>0.1217920271555582</v>
       </c>
       <c r="O5" t="n">
-        <v>25.22786474227905</v>
+        <v>35.49314737319946</v>
       </c>
       <c r="P5" t="n">
-        <v>138.4898929595947</v>
+        <v>55.87785387039185</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.71296358108521</v>
+        <v>36.53760814666748</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-202851</t>
+          <t>20250725-164950</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>5930.014114379883</v>
+        <v>8744.740905046463</v>
       </c>
       <c r="D6" t="n">
-        <v>10.13000011444092</v>
+        <v>23.20999908447266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.317730039358139</v>
+        <v>0.6407642229910819</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5580021739006042</v>
+        <v>0.6358588337898254</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5223520398139954</v>
+        <v>0.5979641675949097</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5209521055221558</v>
+        <v>0.5986061096191406</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5222752690315247</v>
+        <v>0.5950090289115906</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1325315237045288</v>
+        <v>0.1413213908672332</v>
       </c>
       <c r="K6" t="n">
-        <v>660.1953854560852</v>
+        <v>1107.350224971771</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08263966798782341</v>
+        <v>0.1216340271631876</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4597834626833598</v>
+        <v>0.1863974666595459</v>
       </c>
       <c r="N6" t="n">
-        <v>0.146481610139211</v>
+        <v>0.1253077967961629</v>
       </c>
       <c r="O6" t="n">
-        <v>24.79190039634705</v>
+        <v>36.4902081489563</v>
       </c>
       <c r="P6" t="n">
-        <v>137.9350388050079</v>
+        <v>55.91923999786377</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.94448304176331</v>
+        <v>37.59233903884888</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-222442</t>
+          <t>20250725-183446</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>2413.977296113968</v>
+        <v>4773.887196302414</v>
       </c>
       <c r="D2" t="n">
-        <v>18.72999954223633</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5596838361687131</v>
+        <v>0.3401338774710893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5984998941421509</v>
+        <v>0.6192465424537659</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5649551749229431</v>
+        <v>0.587147057056427</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5653535127639771</v>
+        <v>0.5847628116607666</v>
       </c>
       <c r="I2" t="n">
-        <v>0.562347948551178</v>
+        <v>0.5806774497032166</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1195242553949356</v>
+        <v>0.1556472182273864</v>
       </c>
       <c r="K2" t="n">
-        <v>1119.744046211243</v>
+        <v>290.4683599472046</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1228559025128682</v>
+        <v>0.1238600707054138</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1871002586682637</v>
+        <v>0.2186154437065124</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1250183041890462</v>
+        <v>0.131643632253011</v>
       </c>
       <c r="O2" t="n">
-        <v>36.85677075386048</v>
+        <v>37.15802121162415</v>
       </c>
       <c r="P2" t="n">
-        <v>56.13007760047913</v>
+        <v>65.58463311195374</v>
       </c>
       <c r="Q2" t="n">
-        <v>37.50549125671387</v>
+        <v>39.49308967590332</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-235343</t>
+          <t>20250727-181921</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>2153.254387378693</v>
+        <v>7514.157484531403</v>
       </c>
       <c r="D3" t="n">
-        <v>17.59000015258789</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5581216439604759</v>
+        <v>0.3393456439177195</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5953518748283386</v>
+        <v>0.6288003325462341</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5641599893569946</v>
+        <v>0.5928741693496704</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5639660358428955</v>
+        <v>0.5941445231437683</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5593887567520142</v>
+        <v>0.5867495536804199</v>
       </c>
       <c r="J3" t="n">
-        <v>0.119962103664875</v>
+        <v>0.1540053039789199</v>
       </c>
       <c r="K3" t="n">
-        <v>1117.214625358582</v>
+        <v>291.7797939777374</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1174555095036824</v>
+        <v>0.1235234451293945</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1848095814387003</v>
+        <v>0.2216344165802002</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1227280886967976</v>
+        <v>0.132087976137797</v>
       </c>
       <c r="O3" t="n">
-        <v>35.23665285110474</v>
+        <v>37.05703353881836</v>
       </c>
       <c r="P3" t="n">
-        <v>55.44287443161011</v>
+        <v>66.49032497406006</v>
       </c>
       <c r="Q3" t="n">
-        <v>36.81842660903931</v>
+        <v>39.62639284133911</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-005556</t>
+          <t>20250727-194712</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>2157.312927961349</v>
+        <v>7987.999910116196</v>
       </c>
       <c r="D4" t="n">
-        <v>15.84000015258789</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5584998540580273</v>
+        <v>0.342857602569792</v>
       </c>
       <c r="F4" t="n">
-        <v>0.595198929309845</v>
+        <v>0.6290276050567627</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5616453886032104</v>
+        <v>0.5968102216720581</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5592285394668579</v>
+        <v>0.5963903069496155</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5587167143821716</v>
+        <v>0.591697633266449</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1181033477187156</v>
+        <v>0.1561783403158188</v>
       </c>
       <c r="K4" t="n">
-        <v>1118.290511131287</v>
+        <v>294.2520370483398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1230121763547261</v>
+        <v>0.1254643122355143</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1842828154563904</v>
+        <v>0.2222069470087687</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1232166258494059</v>
+        <v>0.1360661594072977</v>
       </c>
       <c r="O4" t="n">
-        <v>36.90365290641785</v>
+        <v>37.6392936706543</v>
       </c>
       <c r="P4" t="n">
-        <v>55.28484463691712</v>
+        <v>66.66208410263062</v>
       </c>
       <c r="Q4" t="n">
-        <v>36.96498775482178</v>
+        <v>40.81984782218933</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-015343</t>
+          <t>20250727-220045</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>2280.261173248291</v>
+        <v>4614.437320232391</v>
       </c>
       <c r="D5" t="n">
-        <v>17.93000030517578</v>
+        <v>10.64000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5581104299601387</v>
+        <v>0.3397467626679328</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5992431640625</v>
+        <v>0.6181938648223877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5617898106575012</v>
+        <v>0.5841109156608582</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5623118877410889</v>
+        <v>0.5843697190284729</v>
       </c>
       <c r="I5" t="n">
-        <v>0.562175989151001</v>
+        <v>0.5771216750144958</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1192174553871154</v>
+        <v>0.1546362340450287</v>
       </c>
       <c r="K5" t="n">
-        <v>1119.823230266571</v>
+        <v>287.6542718410492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1197267826398213</v>
+        <v>0.1214686481157938</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1870389103889465</v>
+        <v>0.218756624062856</v>
       </c>
       <c r="N5" t="n">
-        <v>0.122520424524943</v>
+        <v>0.1329800621668497</v>
       </c>
       <c r="O5" t="n">
-        <v>35.91803479194641</v>
+        <v>36.44059443473816</v>
       </c>
       <c r="P5" t="n">
-        <v>56.11167311668396</v>
+        <v>65.62698721885681</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.75612735748291</v>
+        <v>39.89401865005493</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-025137</t>
+          <t>20250728-002216</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>2168.883434295654</v>
+        <v>6775.346263170242</v>
       </c>
       <c r="D6" t="n">
-        <v>17.44000053405762</v>
+        <v>11.6899995803833</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5629525519907475</v>
+        <v>0.3393565960552381</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5932483673095703</v>
+        <v>0.6276927590370178</v>
       </c>
       <c r="G6" t="n">
-        <v>0.554520308971405</v>
+        <v>0.5979830622673035</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5551213622093201</v>
+        <v>0.5998242497444153</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5524736046791077</v>
+        <v>0.5918912887573242</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1166385263204574</v>
+        <v>0.1526968032121658</v>
       </c>
       <c r="K6" t="n">
-        <v>1114.638537406921</v>
+        <v>288.5257422924042</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1228011004130045</v>
+        <v>0.1237750228246053</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1859538563092549</v>
+        <v>0.2217729425430298</v>
       </c>
       <c r="N6" t="n">
-        <v>0.122290727297465</v>
+        <v>0.1338416616121928</v>
       </c>
       <c r="O6" t="n">
-        <v>36.84033012390137</v>
+        <v>37.13250684738159</v>
       </c>
       <c r="P6" t="n">
-        <v>55.78615689277649</v>
+        <v>66.53188276290894</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.6872181892395</v>
+        <v>40.15249848365784</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-035135</t>
+          <t>20250728-014724</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>2317.791641235352</v>
+        <v>6455.093217849731</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47999954223633</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3137887064367533</v>
+        <v>0.2583194437352094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.603883683681488</v>
+        <v>0.5801594853401184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.569894552230835</v>
+        <v>0.550048828125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5707599520683289</v>
+        <v>0.547100305557251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5664076209068298</v>
+        <v>0.5412030816078186</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1234701126813888</v>
+        <v>0.1014332473278045</v>
       </c>
       <c r="K2" t="n">
-        <v>315.754029750824</v>
+        <v>109.0806241035461</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1241315642992655</v>
+        <v>0.1136312850316365</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2218141174316406</v>
+        <v>0.0937960823376973</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1342659044265747</v>
+        <v>0.082182191212972</v>
       </c>
       <c r="O2" t="n">
-        <v>37.23946928977966</v>
+        <v>34.08938550949097</v>
       </c>
       <c r="P2" t="n">
-        <v>66.54423522949219</v>
+        <v>28.1388247013092</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.27977132797241</v>
+        <v>24.6546573638916</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-120824</t>
+          <t>20250728-194740</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>2312.798979997635</v>
+        <v>8155.11670422554</v>
       </c>
       <c r="D3" t="n">
-        <v>10.39000034332275</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3146934825927019</v>
+        <v>0.2625974300115005</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5929640531539917</v>
+        <v>0.5844809412956238</v>
       </c>
       <c r="G3" t="n">
-        <v>0.559521496295929</v>
+        <v>0.5548920035362244</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5589715242385864</v>
+        <v>0.5546579360961914</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5512311458587646</v>
+        <v>0.5444245934486389</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1238724514842033</v>
+        <v>0.1000138744711875</v>
       </c>
       <c r="K3" t="n">
-        <v>330.5312516689301</v>
+        <v>107.7151379585266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1251789895693461</v>
+        <v>0.1116388940811157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2195310886700948</v>
+        <v>0.09447064797083531</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1303790807723999</v>
+        <v>0.0823779471715291</v>
       </c>
       <c r="O3" t="n">
-        <v>37.55369687080383</v>
+        <v>33.49166822433472</v>
       </c>
       <c r="P3" t="n">
-        <v>65.85932660102844</v>
+        <v>28.34119439125061</v>
       </c>
       <c r="Q3" t="n">
-        <v>39.11372423171997</v>
+        <v>24.71338415145874</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-125547</t>
+          <t>20250728-213917</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C4" t="n">
-        <v>2329.687315940857</v>
+        <v>8920.491899251938</v>
       </c>
       <c r="D4" t="n">
-        <v>10.36999988555908</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3156137149780988</v>
+        <v>0.2507361431534474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5976005792617798</v>
+        <v>0.58552086353302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5660690069198608</v>
+        <v>0.5569030046463013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5656836628913879</v>
+        <v>0.553227424621582</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5587512850761414</v>
+        <v>0.5450137257575989</v>
       </c>
       <c r="J4" t="n">
-        <v>0.126383364200592</v>
+        <v>0.09873753786087031</v>
       </c>
       <c r="K4" t="n">
-        <v>341.7785866260529</v>
+        <v>108.7184824943542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1237520106633504</v>
+        <v>0.1123689476648966</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2180120595296224</v>
+        <v>0.0937083522478739</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1311510229110717</v>
+        <v>0.08118720213572179</v>
       </c>
       <c r="O4" t="n">
-        <v>37.12560319900513</v>
+        <v>33.71068429946899</v>
       </c>
       <c r="P4" t="n">
-        <v>65.40361785888672</v>
+        <v>28.11250567436218</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.34530687332153</v>
+        <v>24.35616064071656</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-134318</t>
+          <t>20250728-235911</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>2335.714592695236</v>
+        <v>8831.169272899628</v>
       </c>
       <c r="D5" t="n">
-        <v>10.4399995803833</v>
+        <v>5.440000057220459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3153963945806026</v>
+        <v>0.2661464127737122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6007556915283203</v>
+        <v>0.5842491984367371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5731163620948792</v>
+        <v>0.5538245439529419</v>
       </c>
       <c r="H5" t="n">
-        <v>0.571394681930542</v>
+        <v>0.5551431775093079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5663905143737793</v>
+        <v>0.5391829609870911</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1260918229818344</v>
+        <v>0.09851637482643121</v>
       </c>
       <c r="K5" t="n">
-        <v>343.8597435951233</v>
+        <v>108.7147741317749</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1200536521275838</v>
+        <v>0.11256432056427</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2181100869178772</v>
+        <v>0.09416117191314689</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1303683217366536</v>
+        <v>0.0810699152946472</v>
       </c>
       <c r="O5" t="n">
-        <v>36.01609563827515</v>
+        <v>33.76929616928101</v>
       </c>
       <c r="P5" t="n">
-        <v>65.43302607536316</v>
+        <v>28.24835157394409</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.11049652099609</v>
+        <v>24.32097458839417</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-143116</t>
+          <t>20250729-023152</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>2341.515309333801</v>
+        <v>6287.030447483063</v>
       </c>
       <c r="D6" t="n">
-        <v>10.34000015258789</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3158606197685003</v>
+        <v>0.255541211201085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6089234948158264</v>
+        <v>0.5808711051940918</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5766128897666931</v>
+        <v>0.5533972978591919</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5749686360359192</v>
+        <v>0.552373468875885</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5694378614425659</v>
+        <v>0.5456122159957886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1282819658517837</v>
+        <v>0.1010908409953117</v>
       </c>
       <c r="K6" t="n">
-        <v>326.0878484249115</v>
+        <v>109.1079788208008</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1223785320917765</v>
+        <v>0.1136925848325093</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2205429442723592</v>
+        <v>0.09439275662104279</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1339391160011291</v>
+        <v>0.08256459951400751</v>
       </c>
       <c r="O6" t="n">
-        <v>36.71355962753296</v>
+        <v>34.10777544975281</v>
       </c>
       <c r="P6" t="n">
-        <v>66.16288328170776</v>
+        <v>28.31782698631286</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.18173480033875</v>
+        <v>24.76937985420227</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-151922</t>
+          <t>20250729-050303</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>1958.86676478386</v>
+        <v>4515.83857178688</v>
       </c>
       <c r="D2" t="n">
-        <v>3.75</v>
+        <v>8.109999656677246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.257675040513277</v>
+        <v>0.2870578450816018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5378779172897339</v>
+        <v>0.6212016344070435</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5073570609092712</v>
+        <v>0.5892656445503235</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5075358748435974</v>
+        <v>0.5907542109489441</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5020542740821838</v>
+        <v>0.5768323540687561</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1104498580098152</v>
+        <v>0.1099173128604888</v>
       </c>
       <c r="K2" t="n">
-        <v>109.4898521900177</v>
+        <v>204.9303455352783</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1186204131444295</v>
+        <v>0.1132023620605468</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09147045771280921</v>
+        <v>0.1418985970815023</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0829680426915486</v>
+        <v>0.1116086554527282</v>
       </c>
       <c r="O2" t="n">
-        <v>35.58612394332886</v>
+        <v>33.96070861816406</v>
       </c>
       <c r="P2" t="n">
-        <v>27.44113731384277</v>
+        <v>42.56957912445069</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.8904128074646</v>
+        <v>33.48259663581848</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-004308</t>
+          <t>20250729-233024</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>1970.197630882263</v>
+        <v>5225.437672615051</v>
       </c>
       <c r="D3" t="n">
-        <v>3.789999961853027</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2626007627695799</v>
+        <v>0.2827877642177954</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5343053340911865</v>
+        <v>0.6311702132225037</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5000377893447876</v>
+        <v>0.5952495932579041</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4986866116523742</v>
+        <v>0.5954943895339966</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4841755628585815</v>
+        <v>0.5845586657524109</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1083417534828186</v>
+        <v>0.1071008518338203</v>
       </c>
       <c r="K3" t="n">
-        <v>109.0522577762604</v>
+        <v>208.7629733085632</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1115067990620931</v>
+        <v>0.1169338448842366</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0913538471857706</v>
+        <v>0.1417648379007975</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0790213418006897</v>
+        <v>0.1110138519605</v>
       </c>
       <c r="O3" t="n">
-        <v>33.45203971862793</v>
+        <v>35.080153465271</v>
       </c>
       <c r="P3" t="n">
-        <v>27.4061541557312</v>
+        <v>42.52945137023926</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.70640254020691</v>
+        <v>33.30415558815002</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-011951</t>
+          <t>20250730-005150</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>1951.416085481644</v>
+        <v>6139.148369073868</v>
       </c>
       <c r="D4" t="n">
-        <v>3.660000085830689</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.256844044663012</v>
+        <v>0.278263297616219</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5441890954971313</v>
+        <v>0.6312462687492371</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5149514675140381</v>
+        <v>0.5949592590332031</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5135014653205872</v>
+        <v>0.5943528413772583</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4617370069026947</v>
+        <v>0.588139533996582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1103233844041824</v>
+        <v>0.1084586083889007</v>
       </c>
       <c r="K4" t="n">
-        <v>108.0146827697754</v>
+        <v>204.7662963867188</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1161817582448323</v>
+        <v>0.1177553025881449</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09215883175532021</v>
+        <v>0.1447271768252054</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0776967843373616</v>
+        <v>0.1154812836647033</v>
       </c>
       <c r="O4" t="n">
-        <v>34.85452747344971</v>
+        <v>35.32659077644348</v>
       </c>
       <c r="P4" t="n">
-        <v>27.64764952659607</v>
+        <v>43.41815304756165</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.3090353012085</v>
+        <v>34.64438509941101</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-015641</t>
+          <t>20250730-022509</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>1952.865256071091</v>
+        <v>6589.596943616867</v>
       </c>
       <c r="D5" t="n">
-        <v>3.690000057220459</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2564958184957504</v>
+        <v>0.2824924393342091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5320150256156921</v>
+        <v>0.6318784356117249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5060157179832458</v>
+        <v>0.5971663594245911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5063496828079224</v>
+        <v>0.598414421081543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4991834163665771</v>
+        <v>0.5833010077476501</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1144177466630935</v>
+        <v>0.1070825979113578</v>
       </c>
       <c r="K5" t="n">
-        <v>108.7669022083282</v>
+        <v>203.4089732170105</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1144542503356933</v>
+        <v>0.1166639097531636</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09325255791346231</v>
+        <v>0.1438981747627258</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0824234676361084</v>
+        <v>0.1130581625302632</v>
       </c>
       <c r="O5" t="n">
-        <v>34.33627510070801</v>
+        <v>34.9991729259491</v>
       </c>
       <c r="P5" t="n">
-        <v>27.9757673740387</v>
+        <v>43.16945242881775</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.72704029083252</v>
+        <v>33.91744875907898</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-023312</t>
+          <t>20250730-041341</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>1948.79149723053</v>
+        <v>6804.961903810501</v>
       </c>
       <c r="D6" t="n">
-        <v>3.619999885559082</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2554693054407835</v>
+        <v>0.2810811422489307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5342319011688232</v>
+        <v>0.6303333044052124</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5075693726539612</v>
+        <v>0.5963138937950134</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5068113207817078</v>
+        <v>0.5975081920623779</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4947678744792938</v>
+        <v>0.582246720790863</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1088498458266258</v>
+        <v>0.1108425930142402</v>
       </c>
       <c r="K6" t="n">
-        <v>109.6725134849548</v>
+        <v>209.8300139904023</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1168923219045003</v>
+        <v>0.1169588414827982</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09575591961542761</v>
+        <v>0.1421354063351949</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08223876078923539</v>
+        <v>0.1119251179695129</v>
       </c>
       <c r="O6" t="n">
-        <v>35.0676965713501</v>
+        <v>35.08765244483948</v>
       </c>
       <c r="P6" t="n">
-        <v>28.7267758846283</v>
+        <v>42.64062190055847</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.67162823677063</v>
+        <v>33.57753539085388</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-030947</t>
+          <t>20250730-060941</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="C2" t="n">
-        <v>2224.728528738022</v>
+        <v>5850.048246383667</v>
       </c>
       <c r="D2" t="n">
-        <v>7.579999923706055</v>
+        <v>11.06999969482422</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2793914149789249</v>
+        <v>0.2591378702673801</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6057885885238647</v>
+        <v>0.4736332893371582</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5764674544334412</v>
+        <v>0.4374872744083404</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5764235258102417</v>
+        <v>0.4367642700672149</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5691007375717163</v>
+        <v>0.4360217154026031</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1098060756921768</v>
+        <v>0.100201316177845</v>
       </c>
       <c r="K2" t="n">
-        <v>204.2879855632782</v>
+        <v>78.61607599258423</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1212529993057251</v>
+        <v>0.0832247964541117</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1429399188359578</v>
+        <v>0.0693501448631286</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1139352893829345</v>
+        <v>0.06434355020523071</v>
       </c>
       <c r="O2" t="n">
-        <v>36.37589979171753</v>
+        <v>24.96743893623352</v>
       </c>
       <c r="P2" t="n">
-        <v>42.88197565078735</v>
+        <v>20.8050434589386</v>
       </c>
       <c r="Q2" t="n">
-        <v>34.18058681488037</v>
+        <v>19.30306506156921</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-142829</t>
+          <t>20250730-172927</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>2088.95799446106</v>
+        <v>4703.933879137039</v>
       </c>
       <c r="D3" t="n">
-        <v>7.849999904632568</v>
+        <v>11.02000045776367</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2767309732735157</v>
+        <v>0.2615949144397956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6096462607383728</v>
+        <v>0.4594686031341553</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5754921436309814</v>
+        <v>0.4287979304790497</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5755579471588135</v>
+        <v>0.4294838011264801</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5646393895149231</v>
+        <v>0.4290326535701751</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1054965034127235</v>
+        <v>0.1010679900646209</v>
       </c>
       <c r="K3" t="n">
-        <v>207.2111883163452</v>
+        <v>80.79058456420898</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1182793911298116</v>
+        <v>0.0810877442359924</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1418108749389648</v>
+        <v>0.0691027903556823</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1119955643018086</v>
+        <v>0.0635749729474385</v>
       </c>
       <c r="O3" t="n">
-        <v>35.48381733894348</v>
+        <v>24.32632327079773</v>
       </c>
       <c r="P3" t="n">
-        <v>42.54326248168945</v>
+        <v>20.73083710670471</v>
       </c>
       <c r="Q3" t="n">
-        <v>33.5986692905426</v>
+        <v>19.07249188423157</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-151148</t>
+          <t>20250730-190956</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>2103.271101474762</v>
+        <v>4998.788552522659</v>
       </c>
       <c r="D4" t="n">
-        <v>7.820000171661377</v>
+        <v>11.07999992370606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2807443346828222</v>
+        <v>0.2575850686108744</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6050732731819153</v>
+        <v>0.467846930027008</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5819476246833801</v>
+        <v>0.4360301494598388</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5812086462974548</v>
+        <v>0.4362393319606781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5723103284835815</v>
+        <v>0.433537483215332</v>
       </c>
       <c r="J4" t="n">
-        <v>0.106391929090023</v>
+        <v>0.0962482616305351</v>
       </c>
       <c r="K4" t="n">
-        <v>205.0905163288116</v>
+        <v>80.38229918479919</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1153911423683166</v>
+        <v>0.0806546552975972</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1391652329762776</v>
+        <v>0.06808469136555979</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1099637532234191</v>
+        <v>0.0608359758059183</v>
       </c>
       <c r="O4" t="n">
-        <v>34.617342710495</v>
+        <v>24.19639658927917</v>
       </c>
       <c r="P4" t="n">
-        <v>41.7495698928833</v>
+        <v>20.42540740966797</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.98912596702576</v>
+        <v>18.25079274177552</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-155252</t>
+          <t>20250730-203121</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
-        <v>2112.658125400543</v>
+        <v>4937.084400892258</v>
       </c>
       <c r="D5" t="n">
-        <v>7.480000019073486</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2815765999257564</v>
+        <v>0.2638652204639382</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6012474894523621</v>
+        <v>0.462662786245346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5707682967185974</v>
+        <v>0.4274135231971741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5689274668693542</v>
+        <v>0.4267420470714569</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5607097148895264</v>
+        <v>0.4266166090965271</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1074445620179176</v>
+        <v>0.1013336852192878</v>
       </c>
       <c r="K5" t="n">
-        <v>208.0423755645752</v>
+        <v>78.50724482536316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1197496628761291</v>
+        <v>0.0825233610471089</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1392122459411621</v>
+        <v>0.0685419996579488</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1095640317598978</v>
+        <v>0.0615624173482259</v>
       </c>
       <c r="O5" t="n">
-        <v>35.92489886283875</v>
+        <v>24.75700831413269</v>
       </c>
       <c r="P5" t="n">
-        <v>41.76367378234863</v>
+        <v>20.56259989738464</v>
       </c>
       <c r="Q5" t="n">
-        <v>32.86920952796936</v>
+        <v>18.46872520446777</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-163406</t>
+          <t>20250730-215739</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>2133.110918998718</v>
+        <v>4879.882606983185</v>
       </c>
       <c r="D6" t="n">
-        <v>7.340000152587891</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2850867267698049</v>
+        <v>0.2601558218399684</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6073193550109863</v>
+        <v>0.4603337049484253</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5734745264053345</v>
+        <v>0.4292641878128052</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5728093981742859</v>
+        <v>0.4301256537437439</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5633301734924316</v>
+        <v>0.42803555727005</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1101973578333854</v>
+        <v>0.09985903650522231</v>
       </c>
       <c r="K6" t="n">
-        <v>204.7646503448486</v>
+        <v>80.81011843681335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1219596942265828</v>
+        <v>0.08156950712203979</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1392339619000752</v>
+        <v>0.0681930176417032</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1102773674329122</v>
+        <v>0.0621879275639851</v>
       </c>
       <c r="O6" t="n">
-        <v>36.58790826797485</v>
+        <v>24.47085213661194</v>
       </c>
       <c r="P6" t="n">
-        <v>41.77018857002258</v>
+        <v>20.45790529251098</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.08321022987366</v>
+        <v>18.65637826919556</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-171533</t>
+          <t>20250730-232254</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>5461.223697662354</v>
+        <v>5000.435883760452</v>
       </c>
       <c r="D2" t="n">
-        <v>4.510000228881836</v>
+        <v>16.05999946594238</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2445005846023559</v>
+        <v>0.3745365887880325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4781939387321472</v>
+        <v>0.5871332883834839</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4495823681354522</v>
+        <v>0.5535126328468323</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4506822526454925</v>
+        <v>0.5476003885269165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4493889510631561</v>
+        <v>0.54414963722229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1628780663013458</v>
+        <v>0.0989775359630584</v>
       </c>
       <c r="K2" t="n">
-        <v>48.66037845611572</v>
+        <v>140.6930334568024</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1041673064231872</v>
+        <v>0.0863579352696736</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0595469403266906</v>
+        <v>0.1368527197837829</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0632150220870971</v>
+        <v>0.0822755908966064</v>
       </c>
       <c r="O2" t="n">
-        <v>31.25019192695618</v>
+        <v>25.9073805809021</v>
       </c>
       <c r="P2" t="n">
-        <v>17.8640820980072</v>
+        <v>41.05581593513489</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.96450662612915</v>
+        <v>24.68267726898193</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-004055</t>
+          <t>20250731-071405</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>5664.315379619598</v>
+        <v>5051.555616378784</v>
       </c>
       <c r="D3" t="n">
-        <v>4.130000114440918</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="E3" t="n">
-        <v>0.242271914696082</v>
+        <v>0.3743415328494289</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4826525747776031</v>
+        <v>0.5873249769210815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4519287645816803</v>
+        <v>0.5584069490432739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4519067108631134</v>
+        <v>0.5564317107200623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.450203388929367</v>
+        <v>0.5535643696784973</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1636677533388137</v>
+        <v>0.1010794565081596</v>
       </c>
       <c r="K3" t="n">
-        <v>49.80025005340576</v>
+        <v>138.8011009693146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1062521243095398</v>
+        <v>0.08696060816446941</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06144518216451</v>
+        <v>0.1390578381220499</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0626281452178955</v>
+        <v>0.0852475508054097</v>
       </c>
       <c r="O3" t="n">
-        <v>31.87563729286194</v>
+        <v>26.08818244934082</v>
       </c>
       <c r="P3" t="n">
-        <v>18.43355464935303</v>
+        <v>41.71735143661499</v>
       </c>
       <c r="Q3" t="n">
-        <v>18.78844356536865</v>
+        <v>25.57426524162292</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-021431</t>
+          <t>20250731-084203</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>4999.285630464554</v>
+        <v>4686.437421560288</v>
       </c>
       <c r="D4" t="n">
-        <v>4.46999979019165</v>
+        <v>17.11000061035156</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2415032779824906</v>
+        <v>0.373976154147454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.478449285030365</v>
+        <v>0.5760749578475952</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4488959014415741</v>
+        <v>0.5440568327903748</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4506013691425323</v>
+        <v>0.5396628975868225</v>
       </c>
       <c r="I4" t="n">
-        <v>0.450301855802536</v>
+        <v>0.5372841358184814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1616256833076477</v>
+        <v>0.1015589982271194</v>
       </c>
       <c r="K4" t="n">
-        <v>48.16920328140259</v>
+        <v>155.5648002624512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1055458291371663</v>
+        <v>0.08717775106430049</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0607725556691487</v>
+        <v>0.1367853665351867</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0631589349110921</v>
+        <v>0.0839987770716349</v>
       </c>
       <c r="O4" t="n">
-        <v>31.6637487411499</v>
+        <v>26.15332531929016</v>
       </c>
       <c r="P4" t="n">
-        <v>18.23176670074463</v>
+        <v>41.03560996055603</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.94768047332764</v>
+        <v>25.19963312149048</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-035132</t>
+          <t>20250731-101050</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>3721.830570459366</v>
+        <v>6757.258258104324</v>
       </c>
       <c r="D5" t="n">
-        <v>3.890000104904175</v>
+        <v>17.27000045776367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2439321478207905</v>
+        <v>0.3729411773867421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4687943160533905</v>
+        <v>0.5932746529579163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.442611813545227</v>
+        <v>0.5593379735946655</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4446151256561279</v>
+        <v>0.5594039559364319</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4331896603107452</v>
+        <v>0.5523656010627747</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1630732417106628</v>
+        <v>0.1022704318165779</v>
       </c>
       <c r="K5" t="n">
-        <v>49.43709707260132</v>
+        <v>154.5893869400024</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1057232403755187</v>
+        <v>0.0866019320487976</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0622295705477396</v>
+        <v>0.1389030679066976</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0617085226376851</v>
+        <v>0.08581082026163731</v>
       </c>
       <c r="O5" t="n">
-        <v>31.71697211265564</v>
+        <v>25.98057961463928</v>
       </c>
       <c r="P5" t="n">
-        <v>18.6688711643219</v>
+        <v>41.67092037200928</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.51255679130555</v>
+        <v>25.74324607849121</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-051727</t>
+          <t>20250731-113349</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>4221.266657829285</v>
+        <v>5497.17099404335</v>
       </c>
       <c r="D6" t="n">
-        <v>3.599999904632568</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2422331101421652</v>
+        <v>0.3744759848040919</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4754723012447357</v>
+        <v>0.5869997143745422</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4416560232639313</v>
+        <v>0.5607608556747437</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4426992237567901</v>
+        <v>0.5573704242706299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.440154105424881</v>
+        <v>0.5530178546905518</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1583129316568374</v>
+        <v>0.099783182144165</v>
       </c>
       <c r="K6" t="n">
-        <v>51.15516591072083</v>
+        <v>138.548353433609</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1066800355911254</v>
+        <v>0.08688070058822631</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0618033496538798</v>
+        <v>0.1381697066624959</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0632752116521199</v>
+        <v>0.085623288154602</v>
       </c>
       <c r="O6" t="n">
-        <v>32.00401067733765</v>
+        <v>26.0642101764679</v>
       </c>
       <c r="P6" t="n">
-        <v>18.54100489616394</v>
+        <v>41.45091199874878</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.98256349563598</v>
+        <v>25.68698644638061</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-062205</t>
+          <t>20250731-133118</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C2" t="n">
-        <v>5690.712840557098</v>
+        <v>3333.572754859924</v>
       </c>
       <c r="D2" t="n">
-        <v>6.269999980926514</v>
+        <v>7.28000020980835</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2597620089848836</v>
+        <v>0.2013163644431242</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4587395489215851</v>
+        <v>0.5078007578849792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4274548292160034</v>
+        <v>0.4755111038684845</v>
       </c>
       <c r="H2" t="n">
-        <v>0.427611380815506</v>
+        <v>0.4747897386550903</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4281980097293854</v>
+        <v>0.4751509428024292</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0952711328864097</v>
+        <v>0.0949224680662155</v>
       </c>
       <c r="K2" t="n">
-        <v>80.76983499526978</v>
+        <v>100.1189095973968</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08258385022481279</v>
+        <v>0.0544432441393534</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06952390193939199</v>
+        <v>0.072392303943634</v>
       </c>
       <c r="N2" t="n">
-        <v>0.063035705089569</v>
+        <v>0.0675287429491678</v>
       </c>
       <c r="O2" t="n">
-        <v>24.77515506744385</v>
+        <v>16.33297324180603</v>
       </c>
       <c r="P2" t="n">
-        <v>20.85717058181763</v>
+        <v>21.71769118309021</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.91071152687073</v>
+        <v>20.25862288475037</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-175537</t>
+          <t>20250627-185631</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>4821.67489695549</v>
+        <v>2687.849930286407</v>
       </c>
       <c r="D3" t="n">
-        <v>6.230000019073486</v>
+        <v>7.309999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2603034028704737</v>
+        <v>0.2002620073380293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4607610702514648</v>
+        <v>0.500224232673645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4276083707809448</v>
+        <v>0.4734110534191131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4287413358688354</v>
+        <v>0.4737220406532287</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4262106716632843</v>
+        <v>0.4724377989768982</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0910926461219787</v>
+        <v>0.1017721444368362</v>
       </c>
       <c r="K3" t="n">
-        <v>79.25774502754211</v>
+        <v>101.1841666698456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0814360491434733</v>
+        <v>0.0571118172009786</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0687042252222697</v>
+        <v>0.0706735587120056</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0625565552711486</v>
+        <v>0.0686127074559529</v>
       </c>
       <c r="O3" t="n">
-        <v>24.43081474304199</v>
+        <v>17.13354516029358</v>
       </c>
       <c r="P3" t="n">
-        <v>20.61126756668091</v>
+        <v>21.20206761360168</v>
       </c>
       <c r="Q3" t="n">
-        <v>18.7669665813446</v>
+        <v>20.58381223678589</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-193329</t>
+          <t>20250627-195525</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>5084.534997940064</v>
+        <v>3009.614695072174</v>
       </c>
       <c r="D4" t="n">
-        <v>6.260000228881836</v>
+        <v>7.269999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2607530959447225</v>
+        <v>0.1993505534578541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4652772545814514</v>
+        <v>0.5077049732208252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4310959875583648</v>
+        <v>0.4778015911579132</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4302084147930145</v>
+        <v>0.4784354269504547</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4298003911972046</v>
+        <v>0.4773849248886108</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0884922891855239</v>
+        <v>0.101452462375164</v>
       </c>
       <c r="K4" t="n">
-        <v>80.49041295051575</v>
+        <v>101.611344575882</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0817766094207763</v>
+        <v>0.0548339525858561</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0687504156430562</v>
+        <v>0.070663358370463</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0630347394943237</v>
+        <v>0.0676269308725992</v>
       </c>
       <c r="O4" t="n">
-        <v>24.53298282623291</v>
+        <v>16.45018577575684</v>
       </c>
       <c r="P4" t="n">
-        <v>20.62512469291687</v>
+        <v>21.19900751113892</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.91042184829712</v>
+        <v>20.28807926177979</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-205650</t>
+          <t>20250627-204334</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" t="n">
-        <v>5238.124736070633</v>
+        <v>3628.10049700737</v>
       </c>
       <c r="D5" t="n">
-        <v>6.190000057220459</v>
+        <v>7.260000228881836</v>
       </c>
       <c r="E5" t="n">
-        <v>0.260876846003842</v>
+        <v>0.2008665640876717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4629315137863159</v>
+        <v>0.5135114789009094</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4307384490966797</v>
+        <v>0.4852354228496551</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4301380217075348</v>
+        <v>0.4859492182731628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4296368062496185</v>
+        <v>0.4844407141208648</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0939663723111152</v>
+        <v>0.096487246453762</v>
       </c>
       <c r="K5" t="n">
-        <v>81.76161217689514</v>
+        <v>101.1971869468689</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08201194365819291</v>
+        <v>0.0553350289662679</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07064172665278109</v>
+        <v>0.0711675302187601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0639519413312276</v>
+        <v>0.0686814864476521</v>
       </c>
       <c r="O5" t="n">
-        <v>24.60358309745789</v>
+        <v>16.60050868988037</v>
       </c>
       <c r="P5" t="n">
-        <v>21.19251799583435</v>
+        <v>21.35025906562805</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.18558239936829</v>
+        <v>20.60444593429565</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-222436</t>
+          <t>20250627-213705</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>5079.656340837479</v>
+        <v>3227.192258358002</v>
       </c>
       <c r="D6" t="n">
-        <v>6.239999771118164</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2597958155473073</v>
+        <v>0.2007171795918391</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4645398259162903</v>
+        <v>0.5094115734100342</v>
       </c>
       <c r="G6" t="n">
-        <v>0.434706836938858</v>
+        <v>0.4765693247318268</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4358070194721222</v>
+        <v>0.477531224489212</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4339599013328552</v>
+        <v>0.4771215617656708</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0892077535390853</v>
+        <v>0.0929730236530304</v>
       </c>
       <c r="K6" t="n">
-        <v>78.80231285095215</v>
+        <v>103.1360576152802</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0817457930246988</v>
+        <v>0.0552577527364095</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0695896530151367</v>
+        <v>0.072851345539093</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0636997469266255</v>
+        <v>0.0682937320073445</v>
       </c>
       <c r="O6" t="n">
-        <v>24.52373790740967</v>
+        <v>16.57732582092285</v>
       </c>
       <c r="P6" t="n">
-        <v>20.87689590454102</v>
+        <v>21.85540366172791</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.10992407798767</v>
+        <v>20.48811960220337</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-235458</t>
+          <t>20250627-224055</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>4615.241571903229</v>
+        <v>5461.223697662354</v>
       </c>
       <c r="D2" t="n">
-        <v>11.90999984741211</v>
+        <v>4.510000228881836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2976798286040624</v>
+        <v>0.2445005846023559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5827236175537109</v>
+        <v>0.4781939387321472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5461341738700867</v>
+        <v>0.4495823681354522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5481788516044617</v>
+        <v>0.4506822526454925</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5439274311065674</v>
+        <v>0.4493889510631561</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07642271369695661</v>
+        <v>0.1628780663013458</v>
       </c>
       <c r="K2" t="n">
-        <v>140.3403668403625</v>
+        <v>48.66037845611572</v>
       </c>
       <c r="L2" t="n">
-        <v>0.089395805199941</v>
+        <v>0.1041673064231872</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1434758901596069</v>
+        <v>0.0595469403266906</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08655890544255571</v>
+        <v>0.0632150220870971</v>
       </c>
       <c r="O2" t="n">
-        <v>26.8187415599823</v>
+        <v>31.25019192695618</v>
       </c>
       <c r="P2" t="n">
-        <v>43.04276704788208</v>
+        <v>17.8640820980072</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.96767163276672</v>
+        <v>18.96450662612915</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-153712</t>
+          <t>20250702-004055</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
-        <v>4713.551789283752</v>
+        <v>5664.315379619598</v>
       </c>
       <c r="D3" t="n">
-        <v>12.57999992370606</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2973757544832845</v>
+        <v>0.242271914696082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5878398418426514</v>
+        <v>0.4826525747776031</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5588881969451904</v>
+        <v>0.4519287645816803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5554492473602295</v>
+        <v>0.4519067108631134</v>
       </c>
       <c r="I3" t="n">
-        <v>0.554872989654541</v>
+        <v>0.450203388929367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07692763954401011</v>
+        <v>0.1636677533388137</v>
       </c>
       <c r="K3" t="n">
-        <v>139.1658573150635</v>
+        <v>49.80025005340576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0864056730270385</v>
+        <v>0.1062521243095398</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1415646807352701</v>
+        <v>0.06144518216451</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0869270912806193</v>
+        <v>0.0626281452178955</v>
       </c>
       <c r="O3" t="n">
-        <v>25.92170190811157</v>
+        <v>31.87563729286194</v>
       </c>
       <c r="P3" t="n">
-        <v>42.46940422058105</v>
+        <v>18.43355464935303</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.07812738418579</v>
+        <v>18.78844356536865</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-165849</t>
+          <t>20250702-021431</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9322,53 +9322,53 @@
         <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>5249.093716859818</v>
+        <v>4999.285630464554</v>
       </c>
       <c r="D4" t="n">
-        <v>11.61999988555908</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2992084600787232</v>
+        <v>0.2415032779824906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5877662301063538</v>
+        <v>0.478449285030365</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5495220422744751</v>
+        <v>0.4488959014415741</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5486223697662354</v>
+        <v>0.4506013691425323</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5443114042282104</v>
+        <v>0.450301855802536</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0774546563625335</v>
+        <v>0.1616256833076477</v>
       </c>
       <c r="K4" t="n">
-        <v>143.78205037117</v>
+        <v>48.16920328140259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08520150581995641</v>
+        <v>0.1055458291371663</v>
       </c>
       <c r="M4" t="n">
-        <v>0.141943552494049</v>
+        <v>0.0607725556691487</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0870371603965759</v>
+        <v>0.0631589349110921</v>
       </c>
       <c r="O4" t="n">
-        <v>25.56045174598694</v>
+        <v>31.6637487411499</v>
       </c>
       <c r="P4" t="n">
-        <v>42.58306574821472</v>
+        <v>18.23176670074463</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.11114811897278</v>
+        <v>18.94768047332764</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-182202</t>
+          <t>20250702-035132</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>4284.151011943817</v>
+        <v>3721.830570459366</v>
       </c>
       <c r="D5" t="n">
-        <v>13.61999988555908</v>
+        <v>3.890000104904175</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2980349910046373</v>
+        <v>0.2439321478207905</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5856850743293762</v>
+        <v>0.4687943160533905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5474042296409607</v>
+        <v>0.442611813545227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5461097955703735</v>
+        <v>0.4446151256561279</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5420464277267456</v>
+        <v>0.4331896603107452</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0770218297839164</v>
+        <v>0.1630732417106628</v>
       </c>
       <c r="K5" t="n">
-        <v>155.177668094635</v>
+        <v>49.43709707260132</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0879782676696777</v>
+        <v>0.1057232403755187</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1411594986915588</v>
+        <v>0.0622295705477396</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0867288732528686</v>
+        <v>0.0617085226376851</v>
       </c>
       <c r="O5" t="n">
-        <v>26.39348030090332</v>
+        <v>31.71697211265564</v>
       </c>
       <c r="P5" t="n">
-        <v>42.34784960746765</v>
+        <v>18.6688711643219</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.0186619758606</v>
+        <v>18.51255679130555</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-195415</t>
+          <t>20250702-051727</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>4766.446066856384</v>
+        <v>4221.266657829285</v>
       </c>
       <c r="D6" t="n">
-        <v>10.36999988555908</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.298908450911122</v>
+        <v>0.2422331101421652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5865355730056763</v>
+        <v>0.4754723012447357</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5505943298339844</v>
+        <v>0.4416560232639313</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5476450324058533</v>
+        <v>0.4426992237567901</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5449560284614563</v>
+        <v>0.440154105424881</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0765114948153495</v>
+        <v>0.1583129316568374</v>
       </c>
       <c r="K6" t="n">
-        <v>139.8139836788177</v>
+        <v>51.15516591072083</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08953473329544059</v>
+        <v>0.1066800355911254</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1401433833440145</v>
+        <v>0.0618033496538798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08560388644536331</v>
+        <v>0.0632752116521199</v>
       </c>
       <c r="O6" t="n">
-        <v>26.8604199886322</v>
+        <v>32.00401067733765</v>
       </c>
       <c r="P6" t="n">
-        <v>42.04301500320435</v>
+        <v>18.54100489616394</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.68116593360901</v>
+        <v>18.98256349563598</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-211035</t>
+          <t>20250702-062205</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
